--- a/experiment/Omni_2CH_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/Omni_2CH_bestx4/Test/results-Set5/Set5.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.78</v>
+        <v>34.87</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9413</v>
+        <v>0.9425</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.54</v>
+        <v>28.61</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9175</v>
+        <v>0.9181</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.93</v>
+        <v>32.94</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7967</v>
+        <v>0.7974</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.63</v>
+        <v>30.69</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9122</v>
+        <v>0.9133</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.13</v>
+        <v>32.18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8924</v>
+        <v>0.8931</v>
       </c>
     </row>
   </sheetData>
